--- a/AAII_Financials/Quarterly/GM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>GM</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>48026000</v>
+      </c>
+      <c r="E8" s="3">
         <v>43624000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45286000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>48591000</v>
       </c>
-      <c r="G8" s="3">
-        <v>47123000</v>
-      </c>
       <c r="H8" s="3">
-        <v>44020000</v>
+        <v>47122000</v>
       </c>
       <c r="I8" s="3">
+        <v>44019000</v>
+      </c>
+      <c r="J8" s="3">
         <v>47702000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>48756000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47970000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43014000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42979000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>44131000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44746000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39985000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43108000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41889000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35759000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35979000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33584000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26779000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34167000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32474000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37518000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>35480000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16778000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32709000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>30826000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>35473000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>36060000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>34878000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>38399000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>35791000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>36760000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>36099000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>37715000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>33623000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>36984000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>37266000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>39896000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>38889000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>33951000</v>
+        <v>40696000</v>
       </c>
       <c r="E9" s="3">
+        <v>35028000</v>
+      </c>
+      <c r="F9" s="3">
         <v>36104000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40344000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39289000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35191000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39447000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39007000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>38615000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33996000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36609000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>35842000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>36632000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32247000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>37305000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36320000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31750000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30879000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29186000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22586000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29160000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27394000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>32721000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>28828000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15782000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>30082000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>29098000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>31161000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>31471000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>31535000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>35092000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>31597000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>33067000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>33198000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>34063000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>29403000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>32210000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>32327000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>35169000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>33341000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6086000</v>
+        <v>3669000</v>
       </c>
       <c r="E10" s="3">
+        <v>5009000</v>
+      </c>
+      <c r="F10" s="3">
         <v>5489000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4714000</v>
       </c>
-      <c r="G10" s="3">
-        <v>4283000</v>
-      </c>
       <c r="H10" s="3">
-        <v>5350000</v>
+        <v>4282000</v>
       </c>
       <c r="I10" s="3">
+        <v>5349000</v>
+      </c>
+      <c r="J10" s="3">
         <v>4540000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6406000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6259000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5944000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3336000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5389000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5383000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5167000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5803000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5569000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4009000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5100000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4398000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4193000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5007000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5080000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4797000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6652000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>996000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2627000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1728000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4312000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4589000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3343000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3307000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4194000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3693000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2901000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3652000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4220000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4774000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4939000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4727000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5548000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,19 +1219,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>8500000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1227,11 +1240,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>9200000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1239,11 +1252,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>9900000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,43 +1467,46 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1077000</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>6034000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1592000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>300000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-96000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>150000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>171000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>77000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1495,11 +1514,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>1168000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1519,17 +1538,17 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1000000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1700000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1546,20 +1565,20 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
@@ -1567,59 +1586,62 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1674000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>888000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1830000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1788000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1731000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1052000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1664000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1699000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1555000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1123000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1771000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1699000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>39541000</v>
+        <v>46488000</v>
       </c>
       <c r="E17" s="3">
+        <v>40618000</v>
+      </c>
+      <c r="F17" s="3">
         <v>42326000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>45834000</v>
       </c>
-      <c r="G17" s="3">
-        <v>44885000</v>
-      </c>
       <c r="H17" s="3">
-        <v>40655000</v>
+        <v>44907000</v>
       </c>
       <c r="I17" s="3">
+        <v>40582000</v>
+      </c>
+      <c r="J17" s="3">
         <v>46830000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44875000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43773000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39245000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42175000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40977000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>41921000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37279000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>41154000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38497000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33643000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33783000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32064000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25134000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31285000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>29197000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34751000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31056000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17992000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>32052000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>31380000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>33169000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>33573000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>33634000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>37570000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>34181000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>35283000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>35570000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>36492000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>31707000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>34687000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>34683000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>38145000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>35741000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4083000</v>
+        <v>1538000</v>
       </c>
       <c r="E18" s="3">
+        <v>3006000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2960000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2757000</v>
       </c>
-      <c r="G18" s="3">
-        <v>2238000</v>
-      </c>
       <c r="H18" s="3">
-        <v>3365000</v>
+        <v>2215000</v>
       </c>
       <c r="I18" s="3">
+        <v>3437000</v>
+      </c>
+      <c r="J18" s="3">
         <v>872000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3881000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4197000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3769000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>804000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3154000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2825000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2706000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1954000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3392000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2116000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2196000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1520000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1645000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2882000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3277000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2767000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4424000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1214000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>657000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-554000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2304000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2487000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1244000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>829000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1610000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1477000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>529000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1223000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1916000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2297000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2583000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1751000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3148000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-326000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1250000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-243000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-436000</v>
-      </c>
       <c r="H20" s="3">
-        <v>-168000</v>
+        <v>-158000</v>
       </c>
       <c r="I20" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="J20" s="3">
         <v>3588000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>82000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>405000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-322000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-217000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-179000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>902000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>964000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>250000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>809000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>944000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1123000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1111000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1164000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>947000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>808000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>625000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>179000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>399000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>484000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>635000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1219000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>814000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1181000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1567000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1197000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1915000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>665000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>802000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1037000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>597000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>606000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6083000</v>
+        <v>3321000</v>
       </c>
       <c r="E21" s="3">
+        <v>5006000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2598000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4830000</v>
       </c>
-      <c r="G21" s="3">
-        <v>4462000</v>
-      </c>
       <c r="H21" s="3">
+        <v>4161000</v>
+      </c>
+      <c r="I21" s="3">
         <v>5264000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1664000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5463000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5491000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5303000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2249000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5142000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4703000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4350000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5626000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7129000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5222000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5896000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5401000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5849000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7011000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7456000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6794000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8394000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2676000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4144000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3131000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6097000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6529000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6579000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5289000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6104000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6173000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5307000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6315000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>5728000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>6293000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>6363000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>5042000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>6288000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E22" s="3">
         <v>158000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>167000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>209000</v>
       </c>
-      <c r="G22" s="3">
-        <v>199000</v>
-      </c>
       <c r="H22" s="3">
+        <v>198000</v>
+      </c>
+      <c r="I22" s="3">
         <v>152000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>215000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>206000</v>
       </c>
       <c r="K22" s="3">
         <v>206000</v>
       </c>
       <c r="L22" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M22" s="3">
         <v>219000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>222000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>229000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>226000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>234000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>268000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>259000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>234000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>226000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>227000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>230000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>243000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>250000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>275000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>327000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>303000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>193000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>200000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>206000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>195000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>181000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>185000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>161000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>159000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>150000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>145000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>151000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>132000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>147000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>150000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>145000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3347000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4248000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1419000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2375000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3572000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2556000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3717000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3643000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3715000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1135000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3464000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3029000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2774000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2588000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4097000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2132000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2779000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2237000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2538000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3750000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4191000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3439000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4905000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-892000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>643000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-355000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2582000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2282000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1458000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2630000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2885000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1576000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2993000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2430000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2967000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3473000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2198000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3609000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E24" s="3">
         <v>642000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-988000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>127000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>481000</v>
       </c>
-      <c r="H24" s="3">
-        <v>719000</v>
-      </c>
       <c r="I24" s="3">
+        <v>718000</v>
+      </c>
+      <c r="J24" s="3">
         <v>318000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>709000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>767000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>762000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-858000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>470000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>522000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>428000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>580000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>845000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>490000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>471000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>152000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>971000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1177000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>642000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>887000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>357000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-163000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>271000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>524000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>137000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-411000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>519000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>466000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>596000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2316000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>534000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>787000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>303000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2705000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3260000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1292000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1894000</v>
       </c>
-      <c r="H26" s="3">
-        <v>2853000</v>
-      </c>
       <c r="I26" s="3">
+        <v>2854000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2874000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3008000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2876000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2953000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1993000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2994000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2507000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2346000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2008000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3252000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1642000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2807000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1766000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2386000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2779000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3014000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2797000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4018000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-780000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>286000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2311000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2403000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2145000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1869000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2530000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2366000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1110000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2397000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>114000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2433000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2686000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1895000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2707000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1287000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2614000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3330000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1297000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1854000</v>
-      </c>
       <c r="H27" s="3">
-        <v>3361000</v>
+        <v>1865000</v>
       </c>
       <c r="I27" s="3">
+        <v>3359000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1725000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3029000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2915000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2970000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2075000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3038000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2540000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2369000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1984000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3278000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1666000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1987000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1696000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2375000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2790000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2976000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2801000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4005000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-806000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>247000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-232000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2313000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2381000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2119000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1806000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2375000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1102000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2412000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>113000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2430000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2677000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1955000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2768000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,14 +3256,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3215,37 +3275,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>200000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-70000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-7577000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-3096000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-770000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-69000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-120000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>326000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1250000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>243000</v>
       </c>
-      <c r="G32" s="3">
-        <v>436000</v>
-      </c>
       <c r="H32" s="3">
-        <v>168000</v>
+        <v>158000</v>
       </c>
       <c r="I32" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3588000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-82000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-405000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>322000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>217000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>179000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>73000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-902000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-964000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-250000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-809000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-944000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1123000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1111000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1164000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-947000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-808000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-625000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-179000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-399000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-484000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-635000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1219000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-814000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1181000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1567000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1197000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1915000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-665000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-802000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1037000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-597000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-606000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2627000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3310000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1327000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1895000</v>
       </c>
-      <c r="H33" s="3">
-        <v>2784000</v>
-      </c>
       <c r="I33" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2961000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3056000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2933000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2980000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3064000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2566000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1984000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3278000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1666000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1987000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1696000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2375000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2790000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2976000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2801000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4005000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-806000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>247000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-232000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2313000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2381000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2119000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2375000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1032000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-5165000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-2983000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1660000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2608000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1835000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2773000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2627000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3310000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1327000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1895000</v>
       </c>
-      <c r="H35" s="3">
-        <v>2784000</v>
-      </c>
       <c r="I35" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2961000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3056000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2933000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2980000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3064000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2566000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1984000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3278000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1666000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1987000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1696000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2375000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2790000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2976000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2801000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4005000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-806000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>247000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-232000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2313000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2381000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2119000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2375000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1032000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-5165000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-2983000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1660000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2608000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1835000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2773000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,1106 +4276,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20134000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19800000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20945000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15110000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13981000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12170000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19872000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18844000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15116000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12635000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13553000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21124000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17874000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13827000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19153000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20745000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16710000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16349000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20067000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17365000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22920000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21609000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19992000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26939000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28228000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38506000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>19069000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20051000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>17072000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17176000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20844000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>18435000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15087000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14256000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>15512000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>12792000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16598000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>12864000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>12574000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>15932000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4585000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4618000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6724000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6792000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6958000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6919000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7265000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8477000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8313000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7845000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7613000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9651000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9556000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9981000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12150000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9566000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10124000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9907000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8609000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6575000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6211000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7771000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9046000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9962000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9254000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7620000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4174000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>6725000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7049000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6021000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5966000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5916000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>6924000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7110000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>8313000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>8454000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>9133000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>10260000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>11841000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>8172000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16770000</v>
+      </c>
+      <c r="E43" s="3">
         <v>16381000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13054000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17125000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16722000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14936000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12827000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13782000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13406000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13774000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12378000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13923000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14068000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13702000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46956000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>45070000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>40896000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>40386000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>34043000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>33184000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32611000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>33709000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>34244000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>34501000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30797000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>33856000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>33398000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>34941000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>38287000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>39346000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>33399000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>33808000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>31668000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>31926000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>28685000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>29412000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>29092000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>34801000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>24827000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>31232000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15950000</v>
+      </c>
+      <c r="E44" s="3">
         <v>15590000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14467000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15318000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15454000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15253000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14564000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17325000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17605000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17533000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16461000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17740000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17912000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17758000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15366000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>16367000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>16859000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>14838000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12988000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>14534000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13102000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>12066000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10235000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10934000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10280000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10799000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10398000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11797000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>11447000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>11108000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>9816000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>11334000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>10833000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>11461000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>10663000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>11789000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>11289000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>14686000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>15427000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4700000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5150000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5399000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5125000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2680000</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5047000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5143000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2395000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1700000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4633000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4680000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4542000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4414000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6826000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6523000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6505000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7114000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6396000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6133000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7765000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6936000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7407000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6841000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8938000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6918000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7953000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7051000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7451000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6439000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5268000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5355000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5939000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6682000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5571000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>14171000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>18969000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>6987000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>15921000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>5733000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>110008000</v>
+      </c>
+      <c r="E46" s="3">
         <v>109121000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108767000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>114636000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>114285000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>110006000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108545000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>115419000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>112064000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106470000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101618000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>110721000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106804000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98832000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100451000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98271000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>91094000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>88594000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>82103000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>77791000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>82609000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>82091000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>80924000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>89177000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>87497000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>97699000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>74992000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>80565000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>81306000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>80090000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>75293000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>74848000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>70451000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>71435000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>68744000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>76618000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>85081000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>79598000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>76203000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>76496000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4485000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4834000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4564000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5177000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4846000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5651000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5896000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9469000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9059000</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8943000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8858000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8397000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8817000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50767000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>49461000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>47960000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>46810000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>45844000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>43879000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>44389000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42668000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>40189000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>38237000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>36723000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>33469000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>34917000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>34239000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>34604000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>33714000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>34298000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>33241000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>31784000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>32029000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>30281000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>29841000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>28385000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>31956000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>25997000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>28944000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53316000</v>
+      </c>
+      <c r="E48" s="3">
         <v>52166000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52683000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51938000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52159000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52128000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52823000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51505000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51145000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51423000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51300000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49399000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>47941000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46895000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>79049000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>76573000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>77250000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>78289000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>80144000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>79294000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>79418000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>78140000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>77451000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>76347000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>76667000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>79265000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>81905000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>81696000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>82082000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>82376000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>82317000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>82783000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>82057000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>80765000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>79135000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>76953000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>74026000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>74504000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>66945000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>66488000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2954000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2987000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3018000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3104000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3142000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3178000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3212000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3399000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3432000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3470000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3508000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3555000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3596000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3618000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4945000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4968000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5013000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5058000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5087000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5126000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5169000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5185000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5230000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5245000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5282000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5225000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5337000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5408000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5457000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5518000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5579000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5651000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5720000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5790000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5849000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5854000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5989000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>6193000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>6149000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6354000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8328000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8542000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7977000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8817000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8943000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7333000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6176000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6944000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6211000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6213000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4767000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7150000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6972000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7329000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28825000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31256000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>32200000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>32741000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31540000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>32467000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30218000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>30327000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31400000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30665000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>31366000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>30966000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>30886000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>29621000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>30288000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>31434000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>29852000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>29188000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>28629000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>28707000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>28473000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>40236000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>46819000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>38542000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>46396000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>39294000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>282742000</v>
+      </c>
+      <c r="E54" s="3">
         <v>280974000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>281284000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>288168000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>289384000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>282104000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>279761000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>289289000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>282956000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>276591000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>273064000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>281705000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>275833000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>267004000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>264037000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>260529000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>253517000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>251492000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>244718000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>238557000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>241803000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>238411000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>235194000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>239671000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>237535000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>246624000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>228037000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>231529000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>233737000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>233132000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>227339000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>225711000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>218641000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>218726000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>212482000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>229502000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>240300000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>230793000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>221690000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>217576000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,263 +6116,270 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28840000</v>
+      </c>
+      <c r="E57" s="3">
         <v>27912000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23919000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27317000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27077000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26948000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25680000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29629000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28762000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29393000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28114000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30387000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29800000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>28931000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27486000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26886000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>25890000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25240000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20391000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18648000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21431000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20446000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19928000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>20914000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15154000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20031000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21018000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21406000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>22717000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>24560000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>22297000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>25147000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>24660000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>26039000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>23929000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>23265000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>23404000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>28725000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>23333000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>28628000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37012000</v>
+      </c>
+      <c r="E58" s="3">
         <v>36294000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35934000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>36477000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>38314000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>35934000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39686000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36162000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38098000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>35976000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>39232000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>38652000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36668000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>37010000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>38778000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>35084000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32306000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>33037000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>33720000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>34819000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>34190000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>35068000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>36913000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>35773000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>40023000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>45061000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>37400000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>34774000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>33149000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>33272000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>31891000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>30865000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>28264000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>29347000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>26965000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>25607000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>30008000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>33701000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>23797000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>25374000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>10259000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -6251,11 +6387,11 @@
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>7925000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -6263,464 +6399,476 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>6086000</v>
       </c>
-      <c r="N59" s="3" t="s">
+      <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3" t="s">
+      <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24909000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24033000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21202000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21278000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20297000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18484000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>19190000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20809000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23069000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23916000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22727000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>26200000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>26487000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>28072000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>28428000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>27471000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>28049000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>28104000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>27368000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>27330000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>25996000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>32977000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>40894000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>28478000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>38051000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>28533000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96834000</v>
+      </c>
+      <c r="E60" s="3">
         <v>94720000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93342000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93295000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93812000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90747000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96265000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95463000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95363000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>91777000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>94445000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96820000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>92718000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90185000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>91173000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>86003000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>79398000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>79555000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>74408000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>71951000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>74811000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>76323000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>79910000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>80603000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>77904000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>91292000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>84905000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>84252000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>84294000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>85303000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>82237000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>84116000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>80292000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>82716000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>76890000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>81849000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>94306000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>90904000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>85181000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>82535000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15465000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15522000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16626000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15690000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15512000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13474000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14288000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15540000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15409000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15949000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16892000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15962000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18859000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18339000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>75921000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>77523000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>78081000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>76768000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>75659000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>74134000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>76698000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>76179000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>72981000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>81793000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>87150000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>81439000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>65924000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>69692000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>73412000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>73812000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>73060000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>71475000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>69995000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>69471000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>67254000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>67066000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>59081000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>57200000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>51326000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>53726000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21924000</v>
+      </c>
+      <c r="E62" s="3">
         <v>20276000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11504000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19272000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18253000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16736000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10281000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15899000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14245000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14890000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9919000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12642000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13062000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12907000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24659000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>27235000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27663000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>28106000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>28836000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>32151000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>32418000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>31466000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>32626000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>29267000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>28988000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>29576000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>31251000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>28814000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>28942000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>29379000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29265000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>29212000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>29718000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>31081000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>32138000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>37110000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>41188000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>36475000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>41108000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>36300000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>219101000</v>
+      </c>
+      <c r="E66" s="3">
         <v>216279000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>218116000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>219766000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>220925000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>215678000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>214171000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>215127000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>211056000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>205990000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>204757000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>202978000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>199861000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>192772000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>196245000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>195260000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>189563000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>189397000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>184974000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>184407000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>190134000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>190068000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>190164000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>196330000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>198231000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>206511000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>186245000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>186975000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>190921000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>192367000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>188479000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>187650000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>182460000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>184428000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>177481000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>187259000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>194779000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>184821000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>177854000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>172856000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>52990000</v>
+      </c>
+      <c r="E72" s="3">
         <v>53386000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51524000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56862000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56675000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55140000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53472000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>62050000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>59807000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>57688000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>55391000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56322000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53517000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51318000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49251000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47910000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>45554000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43879000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41937000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40212000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37806000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34988000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31962000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29134000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>25104000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>25885000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26860000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27609000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25807000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>23939000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22322000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20865000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18873000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>17028000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>17627000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24230000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>28547000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>28195000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>26168000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>25417000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62000000</v>
+      </c>
+      <c r="E76" s="3">
         <v>62659000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>61119000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66374000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66363000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>64372000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63072000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>70935000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>68633000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66598000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>64286000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74475000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71655000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>69877000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>67792000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>65269000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>63954000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62095000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>59744000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>54150000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>51669000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48343000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>45030000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>43341000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>39304000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>40113000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>41792000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>44554000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>42816000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>40765000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>38860000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>38061000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>36181000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>34298000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>35001000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>42243000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>45521000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>45972000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>43836000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>44720000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2627000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3310000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1327000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1895000</v>
       </c>
-      <c r="H81" s="3">
-        <v>2784000</v>
-      </c>
       <c r="I81" s="3">
+        <v>2785000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2961000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3056000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2933000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2980000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3064000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2566000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1984000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3278000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1666000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1987000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1696000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2375000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2790000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2976000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2801000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4005000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-806000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>247000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-232000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2313000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2381000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2119000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2375000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1032000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-5165000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-2983000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1660000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2608000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1835000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2773000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1731000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>906000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1664000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1699000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1555000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1009000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1771000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1699000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1571000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>805000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1572000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1641000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1668000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2770000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2773000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2856000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2891000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2937000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3081000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3018000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3015000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3080000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3162000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3265000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3308000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3286000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3309000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3407000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4116000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3646000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3313000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3129000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3581000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3177000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>3147000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>3054000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2883000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2851000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2686000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6354000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2950000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6795000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7103000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6908000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6061000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4140000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6861000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5976000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3152000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3657000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6596000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7591000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3086000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5624000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5191000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3124000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2104000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6809000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-49000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7162000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1266000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6693000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11231000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2815000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1561000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3473000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6553000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5076000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6030000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3673000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5105000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>448000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6888000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2881000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5518000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2041000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4018000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>6570000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1942000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1512000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3220000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2130000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2137000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1816000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3233000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2245000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2569000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2783000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3706000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2581000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2252000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2431000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6192000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4963000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5381000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4651000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1103000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6118000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1573000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-878000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1972000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-992000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1112000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1224000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2740000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1376000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1462000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2014000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2199000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2079000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2272000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2100000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2167000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-13222000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-14027000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-14028000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4115000</v>
+      </c>
+      <c r="E94" s="3">
         <v>632000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3661000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6668000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4490000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6513000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5017000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5073000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3914000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2563000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5276000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4562000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2262000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6911000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2744000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4318000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3909000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5416000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3929000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4026000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2984000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5007000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4483000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5766000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6570000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1208000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1551000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4429000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3711000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6188000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4535000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5478000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4562000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4811000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-8838000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7118000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-6805000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-11644000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-11660000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E96" s="3">
         <v>223000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>19000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>259000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>85000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>175000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>252000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>76000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>198000</v>
       </c>
-      <c r="M96" s="3" t="s">
+      <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>182000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>126000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>185000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-127000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-189000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-8000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-73000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-16000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-76000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-18000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-76000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-590000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-558000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-608000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-558000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-626000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-552000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-586000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-538000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-566000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-532000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-556000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-572000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-573000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-586000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-594000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2756000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3689000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4999000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5290000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1242000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-543000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1025000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-830000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3493000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8179000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>983000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2528000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1685000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-316000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1461000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1090000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1852000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>532000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1625000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-780000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3617000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8607000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-9557000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>36000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23680000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2332000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2133000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1077000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2842000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3957000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>886000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3769000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-95000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2139000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>5493000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>5047000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>4934000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2120000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E101" s="3">
         <v>51000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-352000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>80000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-153000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-78000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>23000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-77000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>54000</v>
       </c>
       <c r="L101" s="3">
         <v>54000</v>
       </c>
       <c r="M101" s="3">
+        <v>54000</v>
+      </c>
+      <c r="N101" s="3">
         <v>52000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-124000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-159000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>93000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>52000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-124000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-159000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>93000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-34000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-111000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>133000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>182000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>25000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>19000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-448000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>111000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-151000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>42000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-289000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>44000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>153000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>106000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>103000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-297000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-487000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-220000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1925000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>408000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1758000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1079000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3750000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1094000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4243000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-540000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7062000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2226000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5611000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-807000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1551000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3784000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-263000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3564000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1891000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5714000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2489000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1759000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6739000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2784000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8526000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18223000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>44000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2718000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2715000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2638000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3087000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>224000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1968000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3665000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>3999000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>386000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2959000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-2975000</v>
       </c>
     </row>
